--- a/data/b2_indio/B2 Índio 01-2026.xlsx
+++ b/data/b2_indio/B2 Índio 01-2026.xlsx
@@ -4918,7 +4918,7 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>1934.56</v>
+        <v>1784.95</v>
       </c>
     </row>
     <row r="3">
@@ -4936,25 +4936,25 @@
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>51562.3</v>
+        <v>52161.44</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Manutenção preventiva das bombas</t>
+          <t>Seguro do posto</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>2706.97</v>
+        <v>1453.57</v>
       </c>
     </row>
     <row r="5">
@@ -4963,52 +4963,52 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Sistemas e contabilidade</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Seguro do posto</t>
+          <t>Sistema de automação e contabilidade</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>1280.8</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46032</v>
+        <v>46033</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Sistemas e contabilidade</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Sistema de automação e contabilidade</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>3900</v>
+        <v>3383.58</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
-        <v>46033</v>
+        <v>46034</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Uniformes e EPI</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>3291.47</v>
+        <v>1911.86</v>
       </c>
     </row>
     <row r="8">
@@ -5026,7 +5026,7 @@
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>1786.88</v>
+        <v>2147.95</v>
       </c>
     </row>
     <row r="9">
@@ -5044,7 +5044,7 @@
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>10239.81</v>
+        <v>10564.06</v>
       </c>
     </row>
     <row r="10">
@@ -5053,93 +5053,93 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Limpeza da caixa separadora</t>
+          <t>Placas, redes sociais e brindes</t>
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>1793.05</v>
+        <v>1695.88</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="n">
-        <v>46037</v>
+        <v>46040</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Placas, redes sociais e brindes</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>1532.27</v>
+        <v>3274.98</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46040</v>
+        <v>46041</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Uniformes e EPI</t>
+          <t>Limpeza da caixa separadora</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>1301.09</v>
+        <v>3323.18</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>46040</v>
+        <v>46042</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Encargos (INSS e FGTS)</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>3443.68</v>
+        <v>18106.41</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46042</v>
+        <v>46044</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Encargos (INSS e FGTS)</t>
+          <t>Reparo elétrico</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>18365.87</v>
+        <v>2212.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -5148,11 +5148,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Monitoramento e alarme</t>
+          <t>Tarifas bancárias</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>1251.17</v>
+        <v>1011.65</v>
       </c>
     </row>
     <row r="16">
@@ -5170,7 +5170,7 @@
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>3157.97</v>
+        <v>3448.3</v>
       </c>
     </row>
     <row r="17">
@@ -5188,7 +5188,7 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>2837.93</v>
+        <v>2828.99</v>
       </c>
     </row>
   </sheetData>
